--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_7.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02474312102599373</v>
+        <v>0.01949756430837448</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008431038882939211</v>
+        <v>0.008426604091929184</v>
       </c>
       <c r="C2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>30947287</v>
+        <v>4184375</v>
       </c>
       <c r="L2" t="n">
-        <v>16877753</v>
+        <v>2062274</v>
       </c>
       <c r="M2" t="n">
-        <v>4060572</v>
+        <v>448525</v>
       </c>
       <c r="N2" t="n">
-        <v>200059</v>
+        <v>14109</v>
       </c>
       <c r="O2" t="n">
-        <v>2451983</v>
+        <v>269513</v>
       </c>
       <c r="P2" t="n">
-        <v>985067</v>
+        <v>99534</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999900460243225</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8594422936439514</v>
+        <v>0.8000978827476501</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7286285758018494</v>
+        <v>0.6299980282783508</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6554387211799622</v>
+        <v>0.5317251086235046</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3174673020839691</v>
+        <v>0.1165022104978561</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7125651240348816</v>
+        <v>0.5816354751586914</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7984914779663086</v>
+        <v>0.7197275161743164</v>
       </c>
       <c r="X2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44541567</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33971358</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>21009908</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5618737</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>414498</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3217997</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260744</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563041925430298</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114295840263367</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578492999076843</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617420315742493</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019191265106201</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314475059509277</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006213445095175823</v>
+        <v>0.004769023933236478</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002020049719825228</v>
+        <v>0.00201955565764127</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>30947287</v>
+        <v>4184375</v>
       </c>
       <c r="E3" t="n">
-        <v>4377321</v>
+        <v>823925</v>
       </c>
       <c r="F3" t="n">
-        <v>126870</v>
+        <v>24872</v>
       </c>
       <c r="G3" t="n">
-        <v>17883</v>
+        <v>2247</v>
       </c>
       <c r="H3" t="n">
-        <v>7653</v>
+        <v>1556</v>
       </c>
       <c r="I3" t="n">
-        <v>476</v>
+        <v>77</v>
       </c>
       <c r="J3" t="n">
-        <v>70672390</v>
+        <v>10069588</v>
       </c>
       <c r="K3" t="n">
-        <v>74675603</v>
+        <v>10333488</v>
       </c>
       <c r="L3" t="n">
-        <v>85838447</v>
+        <v>11902934</v>
       </c>
       <c r="M3" t="n">
-        <v>106525063</v>
+        <v>15083918</v>
       </c>
       <c r="N3" t="n">
-        <v>114157351</v>
+        <v>16219369</v>
       </c>
       <c r="O3" t="n">
-        <v>110655486</v>
+        <v>15711680</v>
       </c>
       <c r="P3" t="n">
-        <v>113611948</v>
+        <v>16183733</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8723070621490479</v>
+        <v>0.8307180404663086</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7309557795524597</v>
+        <v>0.6245759129524231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6194890141487122</v>
+        <v>0.4786415994167328</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3191059231758118</v>
+        <v>0.1574050337076187</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6868622899055481</v>
+        <v>0.5279785990715027</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7275993824005127</v>
+        <v>0.514369010925293</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33971358</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1397302</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60316</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>48014</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70672833</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>78184653</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>90082731</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107728630</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114375588</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>111294621</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113767753</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575461745262146</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099145531654358</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572057485580444</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611488461494446</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014421701431274</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312224984169006</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06067442982610965</v>
+        <v>0.04997573180022345</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03190669178870938</v>
+        <v>0.0318933357951476</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4757675</v>
+        <v>977363</v>
       </c>
       <c r="E4" t="n">
-        <v>16877753</v>
+        <v>2062274</v>
       </c>
       <c r="F4" t="n">
-        <v>1254628</v>
+        <v>219528</v>
       </c>
       <c r="G4" t="n">
-        <v>66686</v>
+        <v>14950</v>
       </c>
       <c r="H4" t="n">
-        <v>121091</v>
+        <v>25454</v>
       </c>
       <c r="I4" t="n">
-        <v>12118</v>
+        <v>2305</v>
       </c>
       <c r="J4" t="n">
-        <v>443</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>5061282</v>
+        <v>1045454</v>
       </c>
       <c r="L4" t="n">
-        <v>6285974</v>
+        <v>1211187</v>
       </c>
       <c r="M4" t="n">
-        <v>2134625</v>
+        <v>395003</v>
       </c>
       <c r="N4" t="n">
-        <v>430113</v>
+        <v>106996</v>
       </c>
       <c r="O4" t="n">
-        <v>989082</v>
+        <v>193858</v>
       </c>
       <c r="P4" t="n">
-        <v>248593</v>
+        <v>38760</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8658269047737122</v>
+        <v>0.8151204586029053</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7297903299331665</v>
+        <v>0.6272752285003662</v>
       </c>
       <c r="T4" t="n">
-        <v>0.636957049369812</v>
+        <v>0.5037888884544373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3182845115661621</v>
+        <v>0.1338995844125748</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6994776725769043</v>
+        <v>0.5535097122192383</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7613988518714905</v>
+        <v>0.5999619960784912</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1449333</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>21009908</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>583427</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38798</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8037</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1552232</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2041690</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>931058</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211876</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349947</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92788</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569248557090759</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106714725494385</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575274348258972</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614453196525574</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901680588722229</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313349723815918</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>206634</v>
+        <v>48764</v>
       </c>
       <c r="E5" t="n">
-        <v>1604176</v>
+        <v>317214</v>
       </c>
       <c r="F5" t="n">
-        <v>4060572</v>
+        <v>448525</v>
       </c>
       <c r="G5" t="n">
-        <v>155309</v>
+        <v>34017</v>
       </c>
       <c r="H5" t="n">
-        <v>481174</v>
+        <v>79515</v>
       </c>
       <c r="I5" t="n">
-        <v>46834</v>
+        <v>9044</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4530228</v>
+        <v>852683</v>
       </c>
       <c r="L5" t="n">
-        <v>6212226</v>
+        <v>1239605</v>
       </c>
       <c r="M5" t="n">
-        <v>2494140</v>
+        <v>488554</v>
       </c>
       <c r="N5" t="n">
-        <v>426877</v>
+        <v>75526</v>
       </c>
       <c r="O5" t="n">
-        <v>1117849</v>
+        <v>240949</v>
       </c>
       <c r="P5" t="n">
-        <v>368792</v>
+        <v>93973</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999961256980896</v>
+        <v>0.9999980330467224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9167507886886597</v>
+        <v>0.8843727707862854</v>
       </c>
       <c r="S5" t="n">
-        <v>0.891522228717804</v>
+        <v>0.8507071137428284</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9598247408866882</v>
+        <v>0.946177065372467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9925617575645447</v>
+        <v>0.9888814687728882</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9817129373550415</v>
+        <v>0.9735132455825806</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9946414232254028</v>
+        <v>0.9919143915176392</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56771</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>600397</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5618737</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69930</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204446</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1506157</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2080071</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>935975</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>212438</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351835</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93115</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734547734260559</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642252922058105</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983795166015625</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963172078132629</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939088821411133</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983864426612854</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>87104</v>
+        <v>16389</v>
       </c>
       <c r="E6" t="n">
-        <v>118619</v>
+        <v>21904</v>
       </c>
       <c r="F6" t="n">
-        <v>140700</v>
+        <v>25789</v>
       </c>
       <c r="G6" t="n">
-        <v>200059</v>
+        <v>14109</v>
       </c>
       <c r="H6" t="n">
-        <v>72058</v>
+        <v>10291</v>
       </c>
       <c r="I6" t="n">
-        <v>8317</v>
+        <v>1147</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45736</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37747</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76612</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>414498</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48976</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9601</v>
+        <v>2881</v>
       </c>
       <c r="E7" t="n">
-        <v>172677</v>
+        <v>44490</v>
       </c>
       <c r="F7" t="n">
-        <v>579283</v>
+        <v>116294</v>
       </c>
       <c r="G7" t="n">
-        <v>175345</v>
+        <v>51093</v>
       </c>
       <c r="H7" t="n">
-        <v>2451983</v>
+        <v>269513</v>
       </c>
       <c r="I7" t="n">
-        <v>180848</v>
+        <v>26187</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5677</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>208385</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53273</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3217997</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84304</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>203</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>268</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>13181</v>
+        <v>3654</v>
       </c>
       <c r="F8" t="n">
-        <v>33144</v>
+        <v>8520</v>
       </c>
       <c r="G8" t="n">
-        <v>14890</v>
+        <v>4689</v>
       </c>
       <c r="H8" t="n">
-        <v>307106</v>
+        <v>77042</v>
       </c>
       <c r="I8" t="n">
-        <v>985067</v>
+        <v>99534</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2318</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1861</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88173</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260744</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
